--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qianqiantong/PycharmProjects/timetable_generation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0A179E-58CE-FF4D-831E-2950EDFC665D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E12148-8FD0-554A-AC91-7703366ADBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BL2010 TEST" sheetId="4" r:id="rId1"/>
